--- a/examples/dima_buyer_20260920.xlsx
+++ b/examples/dima_buyer_20260920.xlsx
@@ -1,17 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rt\Work\Tristan\tristan_tools\examples\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D542C3A5-6BF0-42D5-AFBE-F0A68616F1AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Лист1" sheetId="1" r:id="rId5"/>
+    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="ГЕО Залива" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="28">
   <si>
     <t>EU</t>
   </si>
@@ -50,38 +60,107 @@
   </si>
   <si>
     <t>Крео</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t>DACH</t>
+  </si>
+  <si>
+    <t>TIR2</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Великобритания</t>
+  </si>
+  <si>
+    <t>Австрия</t>
+  </si>
+  <si>
+    <t>Хорватия</t>
+  </si>
+  <si>
+    <t>Италия</t>
+  </si>
+  <si>
+    <t>Ирландия</t>
+  </si>
+  <si>
+    <t>Германия</t>
+  </si>
+  <si>
+    <t>Словакия</t>
+  </si>
+  <si>
+    <t>Джерси</t>
+  </si>
+  <si>
+    <t>Дания</t>
+  </si>
+  <si>
+    <t>Чехия</t>
+  </si>
+  <si>
+    <t>Мальта</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$$]#,##0"/>
     <numFmt numFmtId="165" formatCode="[$$]#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="dd.mm.yyyy"/>
+    <numFmt numFmtId="166" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13.0"/>
+      <sz val="13"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
-      <sz val="13.0"/>
+      <sz val="13"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -90,7 +169,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -105,12 +184,22 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
-    <border/>
+  <borders count="4">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -119,46 +208,62 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="3" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="3" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="3" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -166,7 +271,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -356,169 +461,204 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:S31"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="K1" s="11" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+    </row>
+    <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Q2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="R2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="S2" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="6">
-        <v>46266.0</v>
-      </c>
-      <c r="B3" s="7" t="s">
+    <row r="3" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="5">
+        <v>46266</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="6">
-        <v>46266.0</v>
-      </c>
-      <c r="L3" s="7" t="s">
+      <c r="K3" s="5">
+        <v>46266</v>
+      </c>
+      <c r="L3" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="K29" s="11" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="s">
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="12"/>
+      <c r="P29" s="12"/>
+      <c r="Q29" s="12"/>
+      <c r="R29" s="12"/>
+      <c r="S29" s="12"/>
+    </row>
+    <row r="30" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="G30" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="H30" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I30" s="5" t="s">
+      <c r="I30" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K30" s="2" t="s">
+      <c r="K30" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L30" s="2" t="s">
+      <c r="L30" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M30" s="3" t="s">
+      <c r="M30" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="N30" s="4" t="s">
+      <c r="N30" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O30" s="5" t="s">
+      <c r="O30" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P30" s="4" t="s">
+      <c r="P30" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="Q30" s="5" t="s">
+      <c r="Q30" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="R30" s="4" t="s">
+      <c r="R30" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="S30" s="5" t="s">
+      <c r="S30" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="B31" s="7" t="s">
+    <row r="31" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A31" s="6">
+        <v>1</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="K31" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="L31" s="7" t="s">
+      <c r="K31" s="6">
+        <v>1</v>
+      </c>
+      <c r="L31" s="6" t="s">
         <v>11</v>
       </c>
     </row>
@@ -529,6 +669,84 @@
     <mergeCell ref="A29:I29"/>
     <mergeCell ref="K29:S29"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE8EB542-02FE-4723-8DCA-736E999494B2}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="22.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="12.5703125" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="8"/>
+    </row>
+    <row r="2" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="10"/>
+    </row>
+    <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="10"/>
+    </row>
+    <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/examples/dima_buyer_20260920.xlsx
+++ b/examples/dima_buyer_20260920.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rt\Work\Tristan\tristan_tools\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D542C3A5-6BF0-42D5-AFBE-F0A68616F1AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35B07B55-7791-42F4-96A6-714DBF2A599E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="26">
   <si>
     <t>EU</t>
   </si>
@@ -62,49 +62,43 @@
     <t>Крео</t>
   </si>
   <si>
-    <t>UK</t>
-  </si>
-  <si>
-    <t>DACH</t>
-  </si>
-  <si>
     <t>TIR2</t>
   </si>
   <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>Великобритания</t>
-  </si>
-  <si>
-    <t>Австрия</t>
-  </si>
-  <si>
-    <t>Хорватия</t>
-  </si>
-  <si>
-    <t>Италия</t>
-  </si>
-  <si>
-    <t>Ирландия</t>
-  </si>
-  <si>
-    <t>Германия</t>
-  </si>
-  <si>
-    <t>Словакия</t>
-  </si>
-  <si>
-    <t>Джерси</t>
-  </si>
-  <si>
-    <t>Дания</t>
-  </si>
-  <si>
-    <t>Чехия</t>
-  </si>
-  <si>
-    <t>Мальта</t>
+    <t>норвегия</t>
+  </si>
+  <si>
+    <t>австрия</t>
+  </si>
+  <si>
+    <t>венгрия</t>
+  </si>
+  <si>
+    <t>чехия</t>
+  </si>
+  <si>
+    <t>словакия</t>
+  </si>
+  <si>
+    <t>германия</t>
+  </si>
+  <si>
+    <t>бельгия</t>
+  </si>
+  <si>
+    <t>дания</t>
+  </si>
+  <si>
+    <t>хорватия</t>
+  </si>
+  <si>
+    <t>нидерланды</t>
+  </si>
+  <si>
+    <t>польша</t>
+  </si>
+  <si>
+    <t>TIR1</t>
   </si>
 </sst>
 </file>
@@ -675,76 +669,114 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE8EB542-02FE-4723-8DCA-736E999494B2}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" style="9" customWidth="1"/>
     <col min="3" max="3" width="13.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="12.5703125" style="9"/>
+    <col min="4" max="16384" width="12.5703125" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="D1" s="8"/>
+    </row>
+    <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="B2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="18" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="B3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="8"/>
-    </row>
-    <row r="2" spans="1:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="B4" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="18" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B5" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="B6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="B7" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="10" t="s">
+    </row>
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="10" t="s">
+    </row>
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="10"/>
-    </row>
-    <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+    </row>
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="10"/>
-    </row>
-    <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
